--- a/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="92">
   <si>
     <t>SCBFY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,149 +2126,159 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>114122000</v>
+      </c>
+      <c r="E41" s="3">
         <v>71247000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88424000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>86800000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>96246000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>70425000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>83422000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>64905000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>87518000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>61927000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101460000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>89137000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>114530000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>72229000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>83820000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>316222000</v>
+      </c>
+      <c r="E42" s="3">
         <v>315420000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>273006000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>262449000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>274187000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>262745000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>271595000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>258029000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>242151000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>222785000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>213390000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>195742000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>190910000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>176774000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>195005000</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>422000</v>
+      </c>
+      <c r="E43" s="3">
         <v>517000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>574000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>571000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>572000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>602000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>663000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>517000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>491000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>510000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>484000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>479000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>423000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>445000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2214,258 +2309,276 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>16500</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8163000</v>
+      </c>
+      <c r="E45" s="3">
         <v>807000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7660000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1855000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5602000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>733000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6408000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1103000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6392000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>918000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6135000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5313000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10744000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7691000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6889000</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>469303000</v>
+      </c>
+      <c r="E46" s="3">
         <v>390883000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>397220000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>354800000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>404484000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>337527000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>384140000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>327915000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>357745000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>289244000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>341008500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>293660000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>337114000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>260509000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>311068900</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>145240000</v>
+      </c>
+      <c r="E47" s="3">
         <v>160551000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>168382000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>163777000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>156965000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>152723000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>145576000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>149184000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>153491000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>162237000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>162221000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>158064000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>163813000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>170794000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>174079000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2439000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2427000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2559000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2477000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2506000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2396000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2425000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2283000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2202000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2252000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2274000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2159000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2216000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2289000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5522000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6394000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6268000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6231000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6145000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6091000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5838000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5791000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6279000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6103000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6153000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6214000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5997000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5898000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5891000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5869000</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62853000</v>
+      </c>
+      <c r="E52" s="3">
         <v>82852000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>48656000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>65290000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>46778000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>58462000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27097000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>63696000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39247000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42709000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31914500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>49133000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>39947000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>57383000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>32589100</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>993406000</v>
+      </c>
+      <c r="E54" s="3">
         <v>972907000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>919955000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>913650000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>913936000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>874446000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>849688000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>872173000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>835427000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>812525000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>822844000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>825833000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>838711000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>820678000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>819922000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>612596000</v>
+      </c>
+      <c r="E57" s="3">
         <v>571042000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>582749000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>556287000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>575225000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>519490000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>513554000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>510312000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>518153000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>489077000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>516590000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>482901000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>515094000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>489058000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>503238000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>161656000</v>
+      </c>
+      <c r="E58" s="3">
         <v>104866000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>146344000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>63997000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>152231000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>66768000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>159293000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>71970000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>136736000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>60502000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>137659000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>77876000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>152487000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>59552000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>156326000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>79715000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1553000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>55284000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1949000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56985000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1305000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>52156000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1650000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56633000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1989000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>44481000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1790000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>53647000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2430000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>43509000</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>860365000</v>
+      </c>
+      <c r="E60" s="3">
         <v>683018000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>791982000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>628793000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>790883000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>593342000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>732030000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>590564000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>718107000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>557461000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>705807000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>569105000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>727546000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>556399000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>709049000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>68519000</v>
+      </c>
+      <c r="E61" s="3">
         <v>84491000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>64843000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>84026000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>59905000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>79503000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58320000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>76110000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>57791000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>71857000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>58400000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>80565000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>53145000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>164717000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51916000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7592000</v>
+      </c>
+      <c r="E62" s="3">
         <v>149635000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7469000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>146596000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7481000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>148238000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7221000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>151777000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7376000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>131608000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7331000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>126924000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7524000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>48676000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8026000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>937513000</v>
+      </c>
+      <c r="E66" s="3">
         <v>918222000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>865369000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>860430000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>859266000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>821978000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>798404000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>819437000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>784100000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>761686000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>772491000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>777477000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>789030000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>770667000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>769906000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3534,11 @@
       <c r="Q70" s="3">
         <v>1494000</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>1494000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>30272000</v>
+      </c>
+      <c r="E72" s="3">
         <v>29528000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29573000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29441000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29983000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28808000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28969000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28577000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29381000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28893000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28459000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27782000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>28988000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>28342000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>28067000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>53919000</v>
+      </c>
+      <c r="E76" s="3">
         <v>52712000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52627000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51291000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>52736000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>50565000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>49396000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>50845000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49423000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48940000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48463000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46484000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47821000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48143000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48172000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,8 +4011,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3861,8 +4059,11 @@
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,8 +4309,11 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4143,8 +4359,11 @@
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,8 +4381,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4209,8 +4429,11 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,8 +4529,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4350,8 +4579,11 @@
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,8 +4601,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4416,8 +4649,11 @@
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,8 +4799,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4604,8 +4849,11 @@
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4651,8 +4899,11 @@
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4696,6 +4947,9 @@
         <v>4</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
